--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T15:50:09+00:00</t>
+    <t>2026-09-14T16:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:14:33+00:00</t>
+    <t>2026-09-14T16:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:38:57+00:00</t>
+    <t>2026-09-14T17:04:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T17:04:18+00:00</t>
+    <t>2026-09-14T17:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-icu-score-rass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T17:35:45+00:00</t>
+    <t>2026-09-14T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
